--- a/lai/valuationquan/AILOF/csiAILOFmodel2mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel2mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1154,6 +1154,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1163,7 +1166,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1474,6 +1477,9 @@
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>4893.7540233362733</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
               </c:numCache>
@@ -1517,7 +1523,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1829,6 +1835,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1838,7 +1847,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2149,6 +2158,9 @@
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>7246.1850032321172</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
               </c:numCache>
@@ -2192,7 +2204,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2504,6 +2516,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2513,7 +2528,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2824,6 +2839,9 @@
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>2352.4309798958438</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
               </c:numCache>
@@ -2846,11 +2864,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="602842624"/>
-        <c:axId val="602844544"/>
+        <c:axId val="558975232"/>
+        <c:axId val="558981120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="602842624"/>
+        <c:axId val="558975232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2893,14 +2911,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="602844544"/>
+        <c:crossAx val="558981120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="602844544"/>
+        <c:axId val="558981120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2949,7 +2967,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="602842624"/>
+        <c:crossAx val="558975232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3134,7 +3152,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3446,6 +3464,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3455,7 +3476,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3766,6 +3787,9 @@
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>6052.5924500756464</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
               </c:numCache>
@@ -3809,7 +3833,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4121,6 +4145,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4130,7 +4157,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4442,6 +4469,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>11507.354340016456</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>11552.867619918841</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4484,7 +4514,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4796,6 +4826,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4805,7 +4838,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5117,6 +5150,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>5454.7618899408099</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5500.2751698431948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5138,11 +5174,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426884096"/>
-        <c:axId val="426894080"/>
+        <c:axId val="559164800"/>
+        <c:axId val="559166592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426884096"/>
+        <c:axId val="559164800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5185,14 +5221,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426894080"/>
+        <c:crossAx val="559166592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426894080"/>
+        <c:axId val="559166592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5241,7 +5277,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426884096"/>
+        <c:crossAx val="559164800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5426,7 +5462,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5738,6 +5774,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5747,7 +5786,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6058,6 +6097,9 @@
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>4478.5830960357953</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
               </c:numCache>
@@ -6101,7 +6143,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6413,6 +6455,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6422,7 +6467,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6733,6 +6778,9 @@
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>6735.3146089982411</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
               </c:numCache>
@@ -6776,7 +6824,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7088,6 +7136,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7097,7 +7148,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7408,6 +7459,9 @@
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>2256.7315129624458</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
               </c:numCache>
@@ -7430,11 +7484,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="427037056"/>
-        <c:axId val="427038592"/>
+        <c:axId val="559215360"/>
+        <c:axId val="559216896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="427037056"/>
+        <c:axId val="559215360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7477,14 +7531,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427038592"/>
+        <c:crossAx val="559216896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="427038592"/>
+        <c:axId val="559216896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7533,7 +7587,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427037056"/>
+        <c:crossAx val="559215360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7718,7 +7772,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8030,6 +8084,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8039,7 +8096,7 @@
               <c:f>'model2(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8350,6 +8407,9 @@
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>2280.0747683969207</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
               </c:numCache>
@@ -8393,7 +8453,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8705,6 +8765,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8714,7 +8777,7 @@
               <c:f>'model2(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9025,6 +9088,9 @@
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>3181.8326442193757</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
               </c:numCache>
@@ -9068,7 +9134,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9380,6 +9446,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9389,7 +9458,7 @@
               <c:f>'model2(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9700,6 +9769,9 @@
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>901.75787582245493</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
               </c:numCache>
@@ -9722,11 +9794,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="427087360"/>
-        <c:axId val="427088896"/>
+        <c:axId val="559929216"/>
+        <c:axId val="559930752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="427087360"/>
+        <c:axId val="559929216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9769,14 +9841,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427088896"/>
+        <c:crossAx val="559930752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="427088896"/>
+        <c:axId val="559930752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9825,7 +9897,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427087360"/>
+        <c:crossAx val="559929216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10010,7 +10082,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10322,6 +10394,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10331,7 +10406,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10642,6 +10717,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -10685,7 +10763,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10997,6 +11075,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11006,7 +11087,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11317,6 +11398,9 @@
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1243.9035388429725</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
               </c:numCache>
@@ -11360,7 +11444,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11672,6 +11756,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11681,7 +11768,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11992,6 +12079,9 @@
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>461.2250703448251</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
               </c:numCache>
@@ -12014,11 +12104,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="500828800"/>
-        <c:axId val="500842880"/>
+        <c:axId val="559975424"/>
+        <c:axId val="559981312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="500828800"/>
+        <c:axId val="559975424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12061,14 +12151,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500842880"/>
+        <c:crossAx val="559981312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="500842880"/>
+        <c:axId val="559981312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12117,7 +12207,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500828800"/>
+        <c:crossAx val="559975424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12302,7 +12392,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12614,6 +12704,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12623,7 +12716,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12934,6 +13027,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -12977,7 +13073,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13289,6 +13385,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13298,7 +13397,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13609,6 +13708,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -13652,7 +13754,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13964,6 +14066,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13973,7 +14078,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14284,6 +14389,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -14306,11 +14414,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="500912128"/>
-        <c:axId val="500913664"/>
+        <c:axId val="596119936"/>
+        <c:axId val="596121472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="500912128"/>
+        <c:axId val="596119936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14353,14 +14461,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500913664"/>
+        <c:crossAx val="596121472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="500913664"/>
+        <c:axId val="596121472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14409,7 +14517,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500912128"/>
+        <c:crossAx val="596119936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14594,7 +14702,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14906,6 +15014,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14915,7 +15026,7 @@
               <c:f>'model2(2)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15226,6 +15337,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -15269,7 +15383,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15581,6 +15695,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15590,7 +15707,7 @@
               <c:f>'model2(2)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15901,6 +16018,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -15944,7 +16064,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16256,6 +16376,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16265,7 +16388,7 @@
               <c:f>'model2(2)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16576,6 +16699,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -16598,11 +16724,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501081216"/>
-        <c:axId val="501082752"/>
+        <c:axId val="596178432"/>
+        <c:axId val="596179968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501081216"/>
+        <c:axId val="596178432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16645,14 +16771,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501082752"/>
+        <c:crossAx val="596179968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501082752"/>
+        <c:axId val="596179968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16701,7 +16827,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501081216"/>
+        <c:crossAx val="596178432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16886,7 +17012,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17198,6 +17324,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17207,7 +17336,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17518,6 +17647,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -17561,7 +17693,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17873,6 +18005,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17882,7 +18017,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18193,6 +18328,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -18236,7 +18374,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18548,6 +18686,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18557,7 +18698,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18868,6 +19009,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -18890,11 +19034,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501860608"/>
-        <c:axId val="501866496"/>
+        <c:axId val="620599936"/>
+        <c:axId val="620605824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501860608"/>
+        <c:axId val="620599936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18937,14 +19081,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501866496"/>
+        <c:crossAx val="620605824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501866496"/>
+        <c:axId val="620605824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18993,7 +19137,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501860608"/>
+        <c:crossAx val="620599936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19101,7 +19245,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19144,7 +19288,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19187,7 +19331,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19230,7 +19374,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19273,7 +19417,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19316,7 +19460,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19359,7 +19503,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19402,7 +19546,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19715,7 +19859,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24164,6 +24308,41 @@
         <v>7246.1850032321172</v>
       </c>
     </row>
+    <row r="108" spans="1:11" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>4893.7540233362733</v>
+      </c>
+      <c r="I108" s="22">
+        <v>7246.1850032321172</v>
+      </c>
+      <c r="J108" s="22">
+        <v>2352.4309798958438</v>
+      </c>
+      <c r="K108" s="21">
+        <v>7246.1850032321172</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24180,7 +24359,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29885,6 +30064,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="108" spans="1:15" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>-346.76585417779705</v>
+      </c>
+      <c r="E108" s="22">
+        <v>-144.48576683273356</v>
+      </c>
+      <c r="F108" s="22">
+        <v>160.9721434510864</v>
+      </c>
+      <c r="G108" s="22">
+        <v>386.33315963410723</v>
+      </c>
+      <c r="H108" s="22">
+        <v>6052.5924500756464</v>
+      </c>
+      <c r="I108" s="22">
+        <v>11552.867619918841</v>
+      </c>
+      <c r="J108" s="22">
+        <v>5500.2751698431948</v>
+      </c>
+      <c r="K108" s="21">
+        <v>11166.534460284734</v>
+      </c>
+      <c r="L108" s="26">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N108" s="27">
+        <v>67.765986815617211</v>
+      </c>
+      <c r="O108" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -29903,7 +30129,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35881,6 +36107,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="108" spans="1:16" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>4478.5830960357953</v>
+      </c>
+      <c r="I108" s="22">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="J108" s="22">
+        <v>2256.7315129624458</v>
+      </c>
+      <c r="K108" s="21">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="L108" s="26">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="M108" s="27">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="N108" s="27">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="O108" s="27">
+        <v>67.813131608977557</v>
+      </c>
+      <c r="P108" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -35899,7 +36175,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -40987,6 +41263,47 @@
         <v>3181.8326442193757</v>
       </c>
     </row>
+    <row r="108" spans="1:13" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="20">
+        <v>1994182</v>
+      </c>
+      <c r="E108" s="20">
+        <v>1884119.8412663853</v>
+      </c>
+      <c r="F108" s="21">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22">
+        <v>0</v>
+      </c>
+      <c r="J108" s="22">
+        <v>2280.0747683969207</v>
+      </c>
+      <c r="K108" s="22">
+        <v>3181.8326442193757</v>
+      </c>
+      <c r="L108" s="22">
+        <v>901.75787582245493</v>
+      </c>
+      <c r="M108" s="21">
+        <v>3181.8326442193757</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -41005,7 +41322,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -45454,6 +45771,41 @@
         <v>1243.9035388429725</v>
       </c>
     </row>
+    <row r="108" spans="1:11" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1243.9035388429725</v>
+      </c>
+      <c r="J108" s="22">
+        <v>461.2250703448251</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1243.9035388429725</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -45472,7 +45824,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51177,6 +51529,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="108" spans="1:15" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="21">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J108" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L108" s="26">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N108" s="27">
+        <v>67.765986815617211</v>
+      </c>
+      <c r="O108" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -51195,7 +51594,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57172,6 +57571,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="108" spans="1:16" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J108" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L108" s="26">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="M108" s="27">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="N108" s="27">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="O108" s="27">
+        <v>67.813131608977557</v>
+      </c>
+      <c r="P108" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -57190,7 +57639,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -62278,6 +62727,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="108" spans="1:13" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="20">
+        <v>1994182</v>
+      </c>
+      <c r="E108" s="20">
+        <v>1884119.8412663853</v>
+      </c>
+      <c r="F108" s="21">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22">
+        <v>0</v>
+      </c>
+      <c r="J108" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K108" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L108" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M108" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel2mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel2mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1157,6 +1157,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1166,7 +1169,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1480,6 +1483,9 @@
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>4893.7540233362733</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
               </c:numCache>
@@ -1523,7 +1529,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1838,6 +1844,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1847,7 +1856,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2161,6 +2170,9 @@
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>7246.1850032321172</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
               </c:numCache>
@@ -2204,7 +2216,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2519,6 +2531,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2528,7 +2543,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2842,6 +2857,9 @@
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>2352.4309798958438</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
               </c:numCache>
@@ -2864,11 +2882,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558975232"/>
-        <c:axId val="558981120"/>
+        <c:axId val="561850624"/>
+        <c:axId val="561872896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558975232"/>
+        <c:axId val="561850624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2911,14 +2929,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558981120"/>
+        <c:crossAx val="561872896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558981120"/>
+        <c:axId val="561872896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2967,7 +2985,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558975232"/>
+        <c:crossAx val="561850624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3152,7 +3170,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3467,6 +3485,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3476,7 +3497,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3790,6 +3811,9 @@
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>6052.5924500756464</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
               </c:numCache>
@@ -3833,7 +3857,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4148,6 +4172,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4157,7 +4184,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4472,6 +4499,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>11552.867619918841</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>11585.38397723743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4514,7 +4544,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4829,6 +4859,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4838,7 +4871,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5153,6 +5186,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>5500.2751698431948</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5532.791527161784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5174,11 +5210,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559164800"/>
-        <c:axId val="559166592"/>
+        <c:axId val="574156160"/>
+        <c:axId val="574231680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559164800"/>
+        <c:axId val="574156160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5221,14 +5257,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559166592"/>
+        <c:crossAx val="574231680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559166592"/>
+        <c:axId val="574231680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5277,7 +5313,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559164800"/>
+        <c:crossAx val="574156160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5462,7 +5498,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5777,6 +5813,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5786,7 +5825,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6100,6 +6139,9 @@
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>4478.5830960357953</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
               </c:numCache>
@@ -6143,7 +6185,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6458,6 +6500,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6467,7 +6512,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6781,6 +6826,9 @@
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>6735.3146089982411</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
               </c:numCache>
@@ -6824,7 +6872,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7139,6 +7187,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7148,7 +7199,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7462,6 +7513,9 @@
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>2256.7315129624458</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
               </c:numCache>
@@ -7484,11 +7538,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559215360"/>
-        <c:axId val="559216896"/>
+        <c:axId val="574305024"/>
+        <c:axId val="574306560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559215360"/>
+        <c:axId val="574305024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7531,14 +7585,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559216896"/>
+        <c:crossAx val="574306560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559216896"/>
+        <c:axId val="574306560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7587,7 +7641,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559215360"/>
+        <c:crossAx val="574305024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7772,7 +7826,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8087,6 +8141,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8096,7 +8153,7 @@
               <c:f>'model2(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8410,6 +8467,9 @@
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>2280.0747683969207</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
               </c:numCache>
@@ -8453,7 +8513,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8768,6 +8828,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8777,7 +8840,7 @@
               <c:f>'model2(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9091,6 +9154,9 @@
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>3181.8326442193757</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
               </c:numCache>
@@ -9134,7 +9200,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9449,6 +9515,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9458,7 +9527,7 @@
               <c:f>'model2(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9772,6 +9841,9 @@
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>901.75787582245493</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
               </c:numCache>
@@ -9794,11 +9866,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559929216"/>
-        <c:axId val="559930752"/>
+        <c:axId val="575649664"/>
+        <c:axId val="575651200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559929216"/>
+        <c:axId val="575649664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9841,14 +9913,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559930752"/>
+        <c:crossAx val="575651200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559930752"/>
+        <c:axId val="575651200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9897,7 +9969,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559929216"/>
+        <c:crossAx val="575649664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10082,7 +10154,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10397,6 +10469,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10406,7 +10481,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10720,6 +10795,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -10763,7 +10841,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11078,6 +11156,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11087,7 +11168,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11401,6 +11482,9 @@
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1243.9035388429725</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
               </c:numCache>
@@ -11444,7 +11528,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11759,6 +11843,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11768,7 +11855,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12082,6 +12169,9 @@
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>461.2250703448251</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
               </c:numCache>
@@ -12104,11 +12194,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559975424"/>
-        <c:axId val="559981312"/>
+        <c:axId val="575683584"/>
+        <c:axId val="575689472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559975424"/>
+        <c:axId val="575683584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12151,14 +12241,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559981312"/>
+        <c:crossAx val="575689472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559981312"/>
+        <c:axId val="575689472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12207,7 +12297,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559975424"/>
+        <c:crossAx val="575683584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12392,7 +12482,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12707,6 +12797,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12716,7 +12809,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13030,6 +13123,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -13073,7 +13169,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13388,6 +13484,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13397,7 +13496,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13711,6 +13810,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -13754,7 +13856,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14069,6 +14171,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14078,7 +14183,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14392,6 +14497,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -14414,11 +14522,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="596119936"/>
-        <c:axId val="596121472"/>
+        <c:axId val="575783296"/>
+        <c:axId val="575784832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="596119936"/>
+        <c:axId val="575783296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14461,14 +14569,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596121472"/>
+        <c:crossAx val="575784832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="596121472"/>
+        <c:axId val="575784832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14517,7 +14625,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596119936"/>
+        <c:crossAx val="575783296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14702,7 +14810,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15017,6 +15125,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15026,7 +15137,7 @@
               <c:f>'model2(2)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15340,6 +15451,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -15383,7 +15497,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15698,6 +15812,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15707,7 +15824,7 @@
               <c:f>'model2(2)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16021,6 +16138,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -16064,7 +16184,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16379,6 +16499,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16388,7 +16511,7 @@
               <c:f>'model2(2)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16702,6 +16825,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -16724,11 +16850,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="596178432"/>
-        <c:axId val="596179968"/>
+        <c:axId val="575837696"/>
+        <c:axId val="575839232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="596178432"/>
+        <c:axId val="575837696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16771,14 +16897,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596179968"/>
+        <c:crossAx val="575839232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="596179968"/>
+        <c:axId val="575839232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16827,7 +16953,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596178432"/>
+        <c:crossAx val="575837696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17012,7 +17138,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17327,6 +17453,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17336,7 +17465,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17650,6 +17779,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -17693,7 +17825,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18008,6 +18140,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18017,7 +18152,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18331,6 +18466,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -18374,7 +18512,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18689,6 +18827,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18698,7 +18839,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19012,6 +19153,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -19034,11 +19178,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="620599936"/>
-        <c:axId val="620605824"/>
+        <c:axId val="585050752"/>
+        <c:axId val="585056640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="620599936"/>
+        <c:axId val="585050752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19081,14 +19225,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620605824"/>
+        <c:crossAx val="585056640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="620605824"/>
+        <c:axId val="585056640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19137,7 +19281,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620599936"/>
+        <c:crossAx val="585050752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19245,7 +19389,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19288,7 +19432,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19331,7 +19475,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19374,7 +19518,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19417,7 +19561,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19460,7 +19604,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19503,7 +19647,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19546,7 +19690,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19859,7 +20003,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24343,6 +24487,41 @@
         <v>7246.1850032321172</v>
       </c>
     </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>4893.7540233362733</v>
+      </c>
+      <c r="I109" s="22">
+        <v>7246.1850032321172</v>
+      </c>
+      <c r="J109" s="22">
+        <v>2352.4309798958438</v>
+      </c>
+      <c r="K109" s="21">
+        <v>7246.1850032321172</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24359,7 +24538,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30111,6 +30290,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="109" spans="1:15" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>-405.63347659313405</v>
+      </c>
+      <c r="E109" s="22">
+        <v>-155.89295806705468</v>
+      </c>
+      <c r="F109" s="22">
+        <v>5.0791853840317174</v>
+      </c>
+      <c r="G109" s="22">
+        <v>13.216040359562751</v>
+      </c>
+      <c r="H109" s="22">
+        <v>6052.5924500756464</v>
+      </c>
+      <c r="I109" s="22">
+        <v>11585.38397723743</v>
+      </c>
+      <c r="J109" s="22">
+        <v>5532.791527161784</v>
+      </c>
+      <c r="K109" s="21">
+        <v>11572.167936877868</v>
+      </c>
+      <c r="L109" s="26">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.035028220618088</v>
+      </c>
+      <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -30129,7 +30355,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36157,6 +36383,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="109" spans="1:16" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>4478.5830960357953</v>
+      </c>
+      <c r="I109" s="22">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="J109" s="22">
+        <v>2256.7315129624458</v>
+      </c>
+      <c r="K109" s="21">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="L109" s="26">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="M109" s="27">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="O109" s="27">
+        <v>78.982013449904031</v>
+      </c>
+      <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -36175,7 +36451,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41304,6 +41580,47 @@
         <v>3181.8326442193757</v>
       </c>
     </row>
+    <row r="109" spans="1:13" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="20">
+        <v>1392651</v>
+      </c>
+      <c r="E109" s="20">
+        <v>1884139.3069248656</v>
+      </c>
+      <c r="F109" s="21">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22">
+        <v>2280.0747683969207</v>
+      </c>
+      <c r="K109" s="22">
+        <v>3181.8326442193757</v>
+      </c>
+      <c r="L109" s="22">
+        <v>901.75787582245493</v>
+      </c>
+      <c r="M109" s="21">
+        <v>3181.8326442193757</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -41322,7 +41639,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -45806,6 +46123,41 @@
         <v>1243.9035388429725</v>
       </c>
     </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1243.9035388429725</v>
+      </c>
+      <c r="J109" s="22">
+        <v>461.2250703448251</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1243.9035388429725</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -45824,7 +46176,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51576,6 +51928,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="109" spans="1:15" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="21">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J109" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L109" s="26">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.035028220618088</v>
+      </c>
+      <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -51594,7 +51993,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57621,6 +58020,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="109" spans="1:16" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J109" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L109" s="26">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="M109" s="27">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="O109" s="27">
+        <v>78.982013449904031</v>
+      </c>
+      <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -57639,7 +58088,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -62768,6 +63217,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="109" spans="1:13" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="20">
+        <v>1392651</v>
+      </c>
+      <c r="E109" s="20">
+        <v>1884139.3069248656</v>
+      </c>
+      <c r="F109" s="21">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K109" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L109" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M109" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel2mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel2mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1160,6 +1160,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1169,7 +1172,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1486,6 +1489,9 @@
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>4893.7540233362733</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
               </c:numCache>
@@ -1529,7 +1535,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1847,6 +1853,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1856,7 +1865,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2173,6 +2182,9 @@
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>7246.1850032321172</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
               </c:numCache>
@@ -2216,7 +2228,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2534,6 +2546,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2543,7 +2558,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2860,6 +2875,9 @@
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>2352.4309798958438</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
               </c:numCache>
@@ -2882,11 +2900,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="561850624"/>
-        <c:axId val="561872896"/>
+        <c:axId val="623973504"/>
+        <c:axId val="623975040"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="561850624"/>
+        <c:axId val="623973504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2929,14 +2947,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561872896"/>
+        <c:crossAx val="623975040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="561872896"/>
+        <c:axId val="623975040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2985,7 +3003,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561850624"/>
+        <c:crossAx val="623973504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3170,7 +3188,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3488,6 +3506,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3497,7 +3518,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3814,6 +3835,9 @@
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>6052.5924500756464</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
               </c:numCache>
@@ -3857,7 +3881,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4175,6 +4199,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4184,7 +4211,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4502,6 +4529,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>11585.38397723743</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>11584.987800428717</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4544,7 +4574,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4862,6 +4892,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4871,7 +4904,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5189,6 +5222,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>5532.791527161784</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5532.3953503530702</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5210,11 +5246,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574156160"/>
-        <c:axId val="574231680"/>
+        <c:axId val="447974016"/>
+        <c:axId val="447984000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574156160"/>
+        <c:axId val="447974016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5257,14 +5293,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574231680"/>
+        <c:crossAx val="447984000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574231680"/>
+        <c:axId val="447984000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5313,7 +5349,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574156160"/>
+        <c:crossAx val="447974016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5498,7 +5534,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5816,6 +5852,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5825,7 +5864,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6142,6 +6181,9 @@
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>4478.5830960357953</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
               </c:numCache>
@@ -6185,7 +6227,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6503,6 +6545,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6512,7 +6557,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6829,6 +6874,9 @@
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>6735.3146089982411</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
               </c:numCache>
@@ -6872,7 +6920,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7190,6 +7238,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7199,7 +7250,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7516,6 +7567,9 @@
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>2256.7315129624458</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
               </c:numCache>
@@ -7538,11 +7592,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574305024"/>
-        <c:axId val="574306560"/>
+        <c:axId val="448057344"/>
+        <c:axId val="448058880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574305024"/>
+        <c:axId val="448057344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7585,14 +7639,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574306560"/>
+        <c:crossAx val="448058880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574306560"/>
+        <c:axId val="448058880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7641,7 +7695,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574305024"/>
+        <c:crossAx val="448057344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7826,7 +7880,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8144,6 +8198,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8153,7 +8210,7 @@
               <c:f>'model2(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8470,6 +8527,9 @@
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>2280.0747683969207</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
               </c:numCache>
@@ -8513,7 +8573,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8831,6 +8891,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8840,7 +8903,7 @@
               <c:f>'model2(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9157,6 +9220,9 @@
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>3181.8326442193757</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
               </c:numCache>
@@ -9200,7 +9266,7 @@
               <c:f>'model2(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9518,6 +9584,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9527,7 +9596,7 @@
               <c:f>'model2(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9844,6 +9913,9 @@
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>901.75787582245493</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
               </c:numCache>
@@ -9866,11 +9938,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575649664"/>
-        <c:axId val="575651200"/>
+        <c:axId val="492315776"/>
+        <c:axId val="492317312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575649664"/>
+        <c:axId val="492315776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9913,14 +9985,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575651200"/>
+        <c:crossAx val="492317312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575651200"/>
+        <c:axId val="492317312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9969,7 +10041,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575649664"/>
+        <c:crossAx val="492315776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10154,7 +10226,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10472,6 +10544,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10481,7 +10556,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10798,6 +10873,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -10841,7 +10919,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11159,6 +11237,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11168,7 +11249,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11485,6 +11566,9 @@
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1243.9035388429725</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
               </c:numCache>
@@ -11528,7 +11612,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11846,6 +11930,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11855,7 +11942,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12172,6 +12259,9 @@
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>461.2250703448251</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
               </c:numCache>
@@ -12194,11 +12284,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575683584"/>
-        <c:axId val="575689472"/>
+        <c:axId val="492349696"/>
+        <c:axId val="492351488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575683584"/>
+        <c:axId val="492349696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12241,14 +12331,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575689472"/>
+        <c:crossAx val="492351488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575689472"/>
+        <c:axId val="492351488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12297,7 +12387,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575683584"/>
+        <c:crossAx val="492349696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12482,7 +12572,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12800,6 +12890,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12809,7 +12902,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13126,6 +13219,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -13169,7 +13265,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13487,6 +13583,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13496,7 +13595,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13813,6 +13912,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -13856,7 +13958,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14174,6 +14276,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14183,7 +14288,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14500,6 +14605,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -14522,11 +14630,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575783296"/>
-        <c:axId val="575784832"/>
+        <c:axId val="494525824"/>
+        <c:axId val="500630656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575783296"/>
+        <c:axId val="494525824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14569,14 +14677,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575784832"/>
+        <c:crossAx val="500630656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575784832"/>
+        <c:axId val="500630656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14625,7 +14733,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575783296"/>
+        <c:crossAx val="494525824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14810,7 +14918,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15128,6 +15236,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15137,7 +15248,7 @@
               <c:f>'model2(2)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15454,6 +15565,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -15497,7 +15611,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15815,6 +15929,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15824,7 +15941,7 @@
               <c:f>'model2(2)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16141,6 +16258,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -16184,7 +16304,7 @@
               <c:f>'model2(2)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16502,6 +16622,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16511,7 +16634,7 @@
               <c:f>'model2(2)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16828,6 +16951,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -16850,11 +16976,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="575837696"/>
-        <c:axId val="575839232"/>
+        <c:axId val="500675328"/>
+        <c:axId val="500676864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="575837696"/>
+        <c:axId val="500675328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16897,14 +17023,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575839232"/>
+        <c:crossAx val="500676864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="575839232"/>
+        <c:axId val="500676864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16953,7 +17079,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575837696"/>
+        <c:crossAx val="500675328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17143,7 +17269,7 @@
                   <c:v>42853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42886</c:v>
+                  <c:v>46080</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>42916</c:v>
@@ -17470,319 +17596,319 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57621376243097611</c:v>
+                  <c:v>0.53243165671554316</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.7189492664455148</c:v>
+                  <c:v>7.6751671607300818</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.844583366399293</c:v>
+                  <c:v>13.80080126068386</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.844583366399293</c:v>
+                  <c:v>13.80080126068386</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.844583366399293</c:v>
+                  <c:v>13.80080126068386</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15.988117091151651</c:v>
+                  <c:v>15.944334985436218</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>41.04379200578655</c:v>
+                  <c:v>41.00000990007112</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46.70014581694987</c:v>
+                  <c:v>46.656363711234441</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>57.492905231276332</c:v>
+                  <c:v>57.449123125560902</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>92.2491255464613</c:v>
+                  <c:v>92.205343440745878</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>172.30060647719367</c:v>
+                  <c:v>172.25682437147825</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>228.9714047240133</c:v>
+                  <c:v>228.92762261829787</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>263.30019012675183</c:v>
+                  <c:v>263.25640802103641</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>300.33791455050084</c:v>
+                  <c:v>300.29413244478542</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>303.32313139384269</c:v>
+                  <c:v>303.27934928812726</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>303.32313139384269</c:v>
+                  <c:v>303.27934928812726</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>303.32313139384269</c:v>
+                  <c:v>303.27934928812726</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>305.35027235124119</c:v>
+                  <c:v>305.30649024552577</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>307.33762163901605</c:v>
+                  <c:v>307.29383953330063</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>307.50765051667753</c:v>
+                  <c:v>307.46386841096211</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>307.50765051667753</c:v>
+                  <c:v>307.46386841096211</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>307.50765051667753</c:v>
+                  <c:v>307.46386841096211</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>308.28621714077974</c:v>
+                  <c:v>308.24243503506432</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>313.60003528991899</c:v>
+                  <c:v>313.55625318420357</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>316.4535834723722</c:v>
+                  <c:v>316.40980136665678</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>316.71089770248</c:v>
+                  <c:v>316.66711559676457</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>317.73541628871601</c:v>
+                  <c:v>317.69163418300059</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>317.74076568201389</c:v>
+                  <c:v>317.69698357629846</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>317.75778856327963</c:v>
+                  <c:v>317.71400645756421</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>346.12732616203544</c:v>
+                  <c:v>346.08354405632002</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>346.35166585996393</c:v>
+                  <c:v>346.30788375424851</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>346.43120812626563</c:v>
+                  <c:v>346.38742602055021</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>346.43120812626563</c:v>
+                  <c:v>346.38742602055021</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>347.15757819781584</c:v>
+                  <c:v>347.11379609210042</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>347.83889366468429</c:v>
+                  <c:v>347.79511155896887</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>348.92037187089284</c:v>
+                  <c:v>348.87658976517741</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17830,7 +17956,7 @@
                   <c:v>42853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42886</c:v>
+                  <c:v>46080</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>42916</c:v>
@@ -18157,319 +18283,319 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57959897679041683</c:v>
+                  <c:v>0.53243165671554316</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.702786265389312</c:v>
+                  <c:v>7.6556189453144388</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.866813639893314</c:v>
+                  <c:v>13.819646319818441</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15.066723050895511</c:v>
+                  <c:v>15.019555730820638</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>14.878099706928005</c:v>
+                  <c:v>14.830932386853132</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>16.591992506617576</c:v>
+                  <c:v>16.544825186542703</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.913234124359064</c:v>
+                  <c:v>40.866066804284195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46.351629978355263</c:v>
+                  <c:v>46.304462658280386</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>54.934667542692608</c:v>
+                  <c:v>54.887500222617739</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>88.041732973627546</c:v>
+                  <c:v>87.994565653552684</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>157.37105286259222</c:v>
+                  <c:v>157.32388554251733</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>222.12126229009593</c:v>
+                  <c:v>222.07409497002104</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>246.03684008077505</c:v>
+                  <c:v>245.98967276070016</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>288.00540758373802</c:v>
+                  <c:v>287.95824026366319</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>361.42999729059869</c:v>
+                  <c:v>361.38282997052386</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>398.85880451809669</c:v>
+                  <c:v>398.8116371980218</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>383.26085077798257</c:v>
+                  <c:v>383.21368345790773</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>362.97348804728466</c:v>
+                  <c:v>362.92632072720983</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>370.11821683323473</c:v>
+                  <c:v>370.07104951315989</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>389.42688804439149</c:v>
+                  <c:v>389.3797207243166</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>402.98939610334662</c:v>
+                  <c:v>402.94222878327179</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>422.37345553914224</c:v>
+                  <c:v>422.32628821906735</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>418.14489541840015</c:v>
+                  <c:v>418.09772809832526</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>416.56731887978844</c:v>
+                  <c:v>416.52015155971355</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>443.03688796494799</c:v>
+                  <c:v>442.98972064487316</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>486.16990261094327</c:v>
+                  <c:v>486.12273529086843</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>498.90670154904672</c:v>
+                  <c:v>498.85953422897182</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>499.11365880948654</c:v>
+                  <c:v>499.06649148941165</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>499.19520733105378</c:v>
+                  <c:v>499.14804001097889</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>499.15743304036585</c:v>
+                  <c:v>499.11026572029095</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>499.88046098898616</c:v>
+                  <c:v>499.83329366891127</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>505.05099885998266</c:v>
+                  <c:v>505.00383153990776</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>508.21494193451935</c:v>
+                  <c:v>508.16777461444445</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>508.79682841510925</c:v>
+                  <c:v>508.74966109503436</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>509.51578528070536</c:v>
+                  <c:v>509.46861796063047</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>510.7754646513003</c:v>
+                  <c:v>510.72829733122541</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>511.3962796036538</c:v>
+                  <c:v>511.3491122835789</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>513.4108061014947</c:v>
+                  <c:v>513.36363878141981</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>513.42176781265152</c:v>
+                  <c:v>513.37460049257663</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>513.43840767266863</c:v>
+                  <c:v>513.39124035259374</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>541.76085103878916</c:v>
+                  <c:v>541.71368371871426</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>548.31455391774386</c:v>
+                  <c:v>548.26738659766897</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>548.42358853725318</c:v>
+                  <c:v>548.3764212171784</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>549.25120419774407</c:v>
+                  <c:v>549.20403687766918</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>547.94264608550873</c:v>
+                  <c:v>547.89547876543384</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>548.77457534742291</c:v>
+                  <c:v>548.72740802734802</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>549.57964217181484</c:v>
+                  <c:v>549.53247485173995</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>563.79412403149411</c:v>
+                  <c:v>563.74695671141922</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>576.14629645503999</c:v>
+                  <c:v>576.0991291349651</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18517,7 +18643,7 @@
                   <c:v>42853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42886</c:v>
+                  <c:v>46080</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>42916</c:v>
@@ -18847,316 +18973,316 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.3852143594407247E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.616300105620283E-2</c:v>
+                  <c:v>-1.9548215415643E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.2230273494020736E-2</c:v>
+                  <c:v>1.8845059134580566E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.2221396844962182</c:v>
+                  <c:v>1.2187544701367781</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0335163405287116</c:v>
+                  <c:v>1.0301311261692714</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.60387541546592516</c:v>
+                  <c:v>0.60049020110648499</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.13055788142748526</c:v>
+                  <c:v>-0.13394309578692543</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.34851583859460789</c:v>
+                  <c:v>-0.35190105295405516</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2.5582376885837235</c:v>
+                  <c:v>-2.5616229029431636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-4.2073925728337542</c:v>
+                  <c:v>-4.2107777871931944</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-14.929553614601446</c:v>
+                  <c:v>-14.932938828960914</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-6.8501424339173695</c:v>
+                  <c:v>-6.8535276482768381</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-17.263350045976779</c:v>
+                  <c:v>-17.266735260336247</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-12.332506966762821</c:v>
+                  <c:v>-12.335892181122233</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>58.106865896756005</c:v>
+                  <c:v>58.103480682396594</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>95.535673124254004</c:v>
+                  <c:v>95.532287909894535</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>79.937719384139882</c:v>
+                  <c:v>79.93433416978047</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>57.623215696043474</c:v>
+                  <c:v>57.619830481684062</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>63.682129354476388</c:v>
+                  <c:v>63.678744140116976</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>82.990800565633151</c:v>
+                  <c:v>82.987415351273683</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>96.553308624588283</c:v>
+                  <c:v>96.549923410228871</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>115.9373680603839</c:v>
+                  <c:v>115.93398284602443</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>111.70880793964182</c:v>
+                  <c:v>111.70542272528235</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>110.13123140103011</c:v>
+                  <c:v>110.12784618667064</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>136.60080048618966</c:v>
+                  <c:v>136.59741527183024</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>179.73381513218493</c:v>
+                  <c:v>179.73042991782552</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>191.60600829280901</c:v>
+                  <c:v>191.60262307844954</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>191.68755681437625</c:v>
+                  <c:v>191.68417160001678</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>191.64978252368832</c:v>
+                  <c:v>191.64639730932885</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>191.59424384820642</c:v>
+                  <c:v>191.59085863384695</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>191.45096357006366</c:v>
+                  <c:v>191.4475783557042</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>191.76135846214714</c:v>
+                  <c:v>191.75797324778767</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>192.08593071262925</c:v>
+                  <c:v>192.08254549826978</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>192.00037206169367</c:v>
+                  <c:v>191.9969868473342</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>193.26005143228861</c:v>
+                  <c:v>193.25666621792914</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>193.8808663846421</c:v>
+                  <c:v>193.87748117028264</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>195.67538981277869</c:v>
+                  <c:v>195.67200459841922</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>195.68100213063764</c:v>
+                  <c:v>195.67761691627817</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>195.680619109389</c:v>
+                  <c:v>195.67723389502953</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>195.63352487675371</c:v>
+                  <c:v>195.63013966239424</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>201.96288805777994</c:v>
+                  <c:v>201.95950284342047</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>201.99238041098755</c:v>
+                  <c:v>201.9889951966282</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>202.81999607147844</c:v>
+                  <c:v>202.81661085711897</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>200.78506788769289</c:v>
+                  <c:v>200.78168267333342</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>200.93568168273862</c:v>
+                  <c:v>200.93229646837915</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>200.659270300922</c:v>
+                  <c:v>200.65588508656253</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>197.36714737913957</c:v>
+                  <c:v>197.3637621647801</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>209.71931980268545</c:v>
+                  <c:v>209.71593458832598</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19178,11 +19304,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="585050752"/>
-        <c:axId val="585056640"/>
+        <c:axId val="501036928"/>
+        <c:axId val="501038464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="585050752"/>
+        <c:axId val="501036928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19225,14 +19351,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="585056640"/>
+        <c:crossAx val="501038464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="585056640"/>
+        <c:axId val="501038464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19281,7 +19407,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="585050752"/>
+        <c:crossAx val="501036928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19389,7 +19515,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19432,7 +19558,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19475,7 +19601,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19518,7 +19644,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19561,7 +19687,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19604,7 +19730,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19647,7 +19773,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19690,7 +19816,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20003,7 +20129,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24522,6 +24648,41 @@
         <v>7246.1850032321172</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4893.7540233362733</v>
+      </c>
+      <c r="I110" s="22">
+        <v>7246.1850032321172</v>
+      </c>
+      <c r="J110" s="22">
+        <v>2352.4309798958438</v>
+      </c>
+      <c r="K110" s="21">
+        <v>7246.1850032321172</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24537,8 +24698,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH109"/>
+  <sheetPr codeName="Sheet2">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24645,7 +24808,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5">
         <f>MIN(F:F)</f>
-        <v>0</v>
+        <v>-145.08939735614592</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="4"/>
@@ -30334,6 +30497,53 @@
         <v>73.035028220618088</v>
       </c>
       <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>-379.02549223852623</v>
+      </c>
+      <c r="E110" s="22">
+        <v>-150.16858274017764</v>
+      </c>
+      <c r="F110" s="22">
+        <v>-145.08939735614592</v>
+      </c>
+      <c r="G110" s="22">
+        <v>-366.20562868767797</v>
+      </c>
+      <c r="H110" s="22">
+        <v>6052.5924500756464</v>
+      </c>
+      <c r="I110" s="22">
+        <v>11584.987800428717</v>
+      </c>
+      <c r="J110" s="22">
+        <v>5532.3953503530702</v>
+      </c>
+      <c r="K110" s="21">
+        <v>11951.193429116394</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -30355,7 +30565,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36433,6 +36643,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4478.5830960357953</v>
+      </c>
+      <c r="I110" s="22">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="J110" s="22">
+        <v>2256.7315129624458</v>
+      </c>
+      <c r="K110" s="21">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -36451,7 +36711,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41621,6 +41881,47 @@
         <v>3181.8326442193757</v>
       </c>
     </row>
+    <row r="110" spans="1:13" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="20">
+        <v>665022</v>
+      </c>
+      <c r="E110" s="20">
+        <v>1877770.3918344665</v>
+      </c>
+      <c r="F110" s="21">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22">
+        <v>2280.0747683969207</v>
+      </c>
+      <c r="K110" s="22">
+        <v>3181.8326442193757</v>
+      </c>
+      <c r="L110" s="22">
+        <v>901.75787582245493</v>
+      </c>
+      <c r="M110" s="21">
+        <v>3181.8326442193757</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -41639,7 +41940,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46158,6 +46459,41 @@
         <v>1243.9035388429725</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1243.9035388429725</v>
+      </c>
+      <c r="J110" s="22">
+        <v>461.2250703448251</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1243.9035388429725</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -46176,7 +46512,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51975,6 +52311,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="21">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J110" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -51993,7 +52376,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -58067,6 +58450,56 @@
         <v>78.982013449904031</v>
       </c>
       <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J110" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -58279,68 +58712,68 @@
       </c>
       <c r="AA4" s="7">
         <f>VLOOKUP(Z4,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AB4" s="7">
         <f t="shared" ref="AB4:AB5" si="0">0-AA4</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AC4" s="6">
         <v>43098</v>
       </c>
       <c r="AD4" s="1">
         <f>VLOOKUP(AC4,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AE4" s="1">
         <f t="shared" ref="AE4" si="1">0-AD4</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AF4" s="6">
         <v>43098</v>
       </c>
       <c r="AG4" s="7">
         <f>VLOOKUP(AF4,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AH4" s="7">
         <f t="shared" ref="AH4:AH7" si="2">0-AG4</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="14.1" customHeight="1">
       <c r="A5" s="15">
-        <v>42886</v>
+        <v>46080</v>
       </c>
       <c r="B5" s="25">
-        <v>0.97</v>
+        <v>2.5239999294281006</v>
       </c>
       <c r="C5" s="20">
-        <v>0.99024999999999985</v>
+        <v>1.3013370512393063</v>
       </c>
       <c r="D5" s="20">
-        <v>143931</v>
+        <v>665022</v>
       </c>
       <c r="E5" s="20">
-        <v>2089485.9285714286</v>
+        <v>1877770.3918344665</v>
       </c>
       <c r="F5" s="21">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="22">
-        <v>4.5136191459209246E-2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="22">
-        <v>4.5136191459209246E-2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="22">
         <v>0</v>
@@ -58353,58 +58786,58 @@
         <v>43098</v>
       </c>
       <c r="R5" s="10">
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="S5" s="5">
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="T5" s="5">
-        <v>0.57959897679041683</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="U5" s="5">
-        <v>3.3852143594407247E-3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="5">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="W5" s="9">
-        <v>5.8749279870701368E-3</v>
+        <v>0</v>
       </c>
       <c r="X5" s="9">
-        <v>5.8749279870701368E-3</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="6">
         <v>43462</v>
       </c>
       <c r="AA5" s="7">
         <f>VLOOKUP(Z5,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AB5" s="7">
         <f t="shared" si="0"/>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AC5" s="6">
         <v>43462</v>
       </c>
       <c r="AD5" s="1">
         <f>VLOOKUP(AC5,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AE5" s="1">
         <f t="shared" ref="AE5:AE6" si="3">0-AD5</f>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AF5" s="6">
         <v>43462</v>
       </c>
       <c r="AG5" s="7">
         <f>VLOOKUP(AF5,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AH5" s="7">
         <f t="shared" si="2"/>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="14.1" customHeight="1">
@@ -58424,10 +58857,10 @@
         <v>1521948.92</v>
       </c>
       <c r="F6" s="21">
-        <v>-4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="22">
-        <v>-4.5136191459209246E-2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
@@ -58436,47 +58869,47 @@
         <v>0</v>
       </c>
       <c r="J6" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M6" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="7"/>
       <c r="Q6" s="6">
         <v>43462</v>
       </c>
       <c r="R6" s="10">
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="S6" s="5">
-        <v>263.30019012675183</v>
+        <v>263.25640802103641</v>
       </c>
       <c r="T6" s="5">
-        <v>246.03684008077505</v>
+        <v>245.98967276070016</v>
       </c>
       <c r="U6" s="5">
-        <v>-17.263350045976779</v>
+        <v>-17.266735260336247</v>
       </c>
       <c r="V6" s="5">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="W6" s="9">
-        <v>-6.556527755512162E-2</v>
+        <v>-6.558904070041284E-2</v>
       </c>
       <c r="X6" s="9">
-        <v>-6.5431454731200711E-2</v>
+        <v>-6.5465305989182543E-2</v>
       </c>
       <c r="Z6" s="6">
         <v>43462</v>
       </c>
       <c r="AB6" s="7">
-        <v>246.03684008077505</v>
+        <v>245.98967276070016</v>
       </c>
       <c r="AC6" s="6">
         <v>43830</v>
@@ -58530,16 +58963,16 @@
         <v>0</v>
       </c>
       <c r="J7" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="7"/>
       <c r="Q7" s="6">
@@ -58549,32 +58982,32 @@
         <v>43.135897352006509</v>
       </c>
       <c r="S7" s="5">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="T7" s="5">
-        <v>443.03688796494799</v>
+        <v>442.98972064487316</v>
       </c>
       <c r="U7" s="5">
-        <v>136.60080048618966</v>
+        <v>136.59741527183024</v>
       </c>
       <c r="V7" s="5">
-        <v>103.29053972594444</v>
+        <v>103.24337240586956</v>
       </c>
       <c r="W7" s="9">
-        <v>0.44577256422404427</v>
+        <v>0.4458252145252744</v>
       </c>
       <c r="X7" s="9">
-        <v>0.21756075338951386</v>
+        <v>0.21760724296498135</v>
       </c>
       <c r="AB7" s="8">
         <f>IRR(AB4:AB6)</f>
-        <v>-6.5431454731200711E-2</v>
+        <v>-6.5465305989182543E-2</v>
       </c>
       <c r="AC7" s="6">
         <v>43830</v>
       </c>
       <c r="AE7" s="1">
-        <v>443.03688796494799</v>
+        <v>442.98972064487316</v>
       </c>
       <c r="AF7" s="6">
         <v>44196</v>
@@ -58617,16 +59050,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="7"/>
       <c r="Q8" s="6">
@@ -58636,32 +59069,32 @@
         <v>0</v>
       </c>
       <c r="S8" s="5">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="T8" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="U8" s="5">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="V8" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="W8" s="9">
-        <v>0.62515182688236726</v>
+        <v>0.62523010968710047</v>
       </c>
       <c r="X8" s="9">
-        <v>0.18427566897698489</v>
+        <v>0.18430783116175009</v>
       </c>
       <c r="AE8" s="2">
         <f>IRR(AE4:AE7)</f>
-        <v>0.21756075338951386</v>
+        <v>0.21760724296498135</v>
       </c>
       <c r="AF8" s="6">
         <v>44196</v>
       </c>
       <c r="AH8" s="7">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="14.1" customHeight="1">
@@ -58693,16 +59126,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M9" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="7"/>
       <c r="Q9" s="29">
@@ -58712,26 +59145,26 @@
         <v>0</v>
       </c>
       <c r="S9" s="5">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="T9" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="U9" s="5">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="V9" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="W9" s="9">
-        <v>0.62515182688236726</v>
+        <v>0.62523010968710047</v>
       </c>
       <c r="X9" s="9">
-        <v>0.13374077680861762</v>
+        <v>0.13376124558787272</v>
       </c>
       <c r="AH9" s="2">
         <f>IRR(AH4:AH8)</f>
-        <v>0.18427566897698489</v>
+        <v>0.18430783116175009</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="14.1" customHeight="1">
@@ -58763,16 +59196,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="7"/>
       <c r="Q10" s="29">
@@ -58782,44 +59215,44 @@
         <v>11.079325740253353</v>
       </c>
       <c r="S10" s="5">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="T10" s="5">
-        <v>509.51578528070536</v>
+        <v>509.46861796063047</v>
       </c>
       <c r="U10" s="5">
-        <v>192.00037206169367</v>
+        <v>191.9969868473342</v>
       </c>
       <c r="V10" s="5">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
       <c r="W10" s="9">
-        <v>0.60469622597268413</v>
+        <v>0.60476895580889278</v>
       </c>
       <c r="X10" s="9">
-        <v>0.10458712586200214</v>
+        <v>0.1046018033933096</v>
       </c>
       <c r="Z10" s="6">
         <v>43098</v>
       </c>
       <c r="AA10" s="7">
         <f>VLOOKUP(Z10,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AB10" s="1">
         <f>-AA10</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AC10" s="6">
         <v>43098</v>
       </c>
       <c r="AD10" s="1">
         <f t="shared" ref="AD10:AD15" si="4">VLOOKUP(AC10,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AE10" s="1">
         <f t="shared" ref="AE10:AE15" si="5">-AD10</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AF10" s="6">
         <v>43098</v>
@@ -58861,16 +59294,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M11" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="7"/>
       <c r="Q11" s="29">
@@ -58880,19 +59313,19 @@
         <v>0.24237534426794127</v>
       </c>
       <c r="S11" s="5">
-        <v>317.75778856327963</v>
+        <v>317.71400645756421</v>
       </c>
       <c r="T11" s="5">
-        <v>513.43840767266863</v>
+        <v>513.39124035259374</v>
       </c>
       <c r="U11" s="5">
-        <v>195.680619109389</v>
+        <v>195.67723389502953</v>
       </c>
       <c r="V11" s="5">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="W11" s="9">
-        <v>0.61581690882903517</v>
+        <v>0.61589111565078369</v>
       </c>
       <c r="X11" s="9">
         <v>8.7073790790229921E-2</v>
@@ -58902,22 +59335,22 @@
       </c>
       <c r="AA11" s="7">
         <f>VLOOKUP(Z11,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AB11" s="1">
         <f>-AA11</f>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AC11" s="6">
         <v>43462</v>
       </c>
       <c r="AD11" s="1">
         <f t="shared" si="4"/>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AE11" s="1">
         <f t="shared" si="5"/>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AF11" s="6">
         <v>43462</v>
@@ -58959,16 +59392,16 @@
         <v>0.53243165671554316</v>
       </c>
       <c r="J12" s="22">
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="K12" s="22">
-        <v>0.57959897679041683</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="L12" s="22">
-        <v>3.3852143594407247E-3</v>
+        <v>0</v>
       </c>
       <c r="M12" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="7"/>
       <c r="Q12" s="29">
@@ -58978,19 +59411,19 @@
         <v>48.669188089074908</v>
       </c>
       <c r="S12" s="5">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="T12" s="5">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="U12" s="5">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="V12" s="5">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="W12" s="9">
-        <v>0.58128039180943369</v>
+        <v>0.58134061418189364</v>
       </c>
       <c r="X12" s="9">
         <v>7.7879086338844994E-2</v>
@@ -59057,16 +59490,16 @@
         <v>7.6556189453144388</v>
       </c>
       <c r="J13" s="22">
-        <v>7.7189492664455148</v>
+        <v>7.6751671607300818</v>
       </c>
       <c r="K13" s="22">
-        <v>7.702786265389312</v>
+        <v>7.6556189453144388</v>
       </c>
       <c r="L13" s="22">
-        <v>-1.616300105620283E-2</v>
+        <v>-1.9548215415643E-2</v>
       </c>
       <c r="M13" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="7"/>
       <c r="Z13" s="6">
@@ -59131,16 +59564,16 @@
         <v>13.819646319818441</v>
       </c>
       <c r="J14" s="22">
-        <v>13.844583366399293</v>
+        <v>13.80080126068386</v>
       </c>
       <c r="K14" s="22">
-        <v>13.866813639893314</v>
+        <v>13.819646319818441</v>
       </c>
       <c r="L14" s="22">
-        <v>2.2230273494020736E-2</v>
+        <v>1.8845059134580566E-2</v>
       </c>
       <c r="M14" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="7"/>
       <c r="Z14" s="29">
@@ -59205,23 +59638,23 @@
         <v>8.2164328632246892</v>
       </c>
       <c r="J15" s="22">
-        <v>13.844583366399293</v>
+        <v>13.80080126068386</v>
       </c>
       <c r="K15" s="22">
-        <v>15.066723050895511</v>
+        <v>15.019555730820638</v>
       </c>
       <c r="L15" s="22">
-        <v>1.2221396844962182</v>
+        <v>1.2187544701367781</v>
       </c>
       <c r="M15" s="21">
-        <v>6.8502901876708231</v>
+        <v>6.8031228675959499</v>
       </c>
       <c r="N15" s="7"/>
       <c r="Z15" s="29">
         <v>44561</v>
       </c>
       <c r="AB15" s="7">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="AC15" s="29">
         <v>44925</v>
@@ -59274,27 +59707,27 @@
         <v>7.4940646601115359</v>
       </c>
       <c r="J16" s="22">
-        <v>13.844583366399293</v>
+        <v>13.80080126068386</v>
       </c>
       <c r="K16" s="22">
-        <v>14.878099706928005</v>
+        <v>14.830932386853132</v>
       </c>
       <c r="L16" s="22">
-        <v>1.0335163405287116</v>
+        <v>1.0301311261692714</v>
       </c>
       <c r="M16" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N16" s="7"/>
       <c r="AB16" s="2">
         <f>IRR(AB10:AB15)</f>
-        <v>0.13374077680861762</v>
+        <v>0.13376124558787272</v>
       </c>
       <c r="AC16" s="29">
         <v>44925</v>
       </c>
       <c r="AE16" s="1">
-        <v>509.51578528070536</v>
+        <v>509.46861796063047</v>
       </c>
       <c r="AF16" s="29">
         <v>45289</v>
@@ -59336,21 +59769,21 @@
         <v>9.2079574598011078</v>
       </c>
       <c r="J17" s="22">
-        <v>15.988117091151651</v>
+        <v>15.944334985436218</v>
       </c>
       <c r="K17" s="22">
-        <v>16.591992506617576</v>
+        <v>16.544825186542703</v>
       </c>
       <c r="L17" s="22">
-        <v>0.60387541546592516</v>
+        <v>0.60049020110648499</v>
       </c>
       <c r="M17" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N17" s="7"/>
       <c r="AE17" s="2">
         <f>IRR(AE10:AE16)</f>
-        <v>0.10458712586200214</v>
+        <v>0.1046018033933096</v>
       </c>
       <c r="AF17" s="29">
         <v>45289</v>
@@ -59388,16 +59821,16 @@
         <v>33.5291990775426</v>
       </c>
       <c r="J18" s="22">
-        <v>41.04379200578655</v>
+        <v>41.00000990007112</v>
       </c>
       <c r="K18" s="22">
-        <v>40.913234124359064</v>
+        <v>40.866066804284195</v>
       </c>
       <c r="L18" s="22">
-        <v>-0.13055788142748526</v>
+        <v>-0.13394309578692543</v>
       </c>
       <c r="M18" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N18" s="7"/>
       <c r="AH18" s="2">
@@ -59434,16 +59867,16 @@
         <v>38.967594931538791</v>
       </c>
       <c r="J19" s="22">
-        <v>46.70014581694987</v>
+        <v>46.656363711234441</v>
       </c>
       <c r="K19" s="22">
-        <v>46.351629978355263</v>
+        <v>46.304462658280386</v>
       </c>
       <c r="L19" s="22">
-        <v>-0.34851583859460789</v>
+        <v>-0.35190105295405516</v>
       </c>
       <c r="M19" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N19" s="7"/>
       <c r="Z19" s="6">
@@ -59486,16 +59919,16 @@
         <v>47.550632495876144</v>
       </c>
       <c r="J20" s="22">
-        <v>57.492905231276332</v>
+        <v>57.449123125560902</v>
       </c>
       <c r="K20" s="22">
-        <v>54.934667542692608</v>
+        <v>54.887500222617739</v>
       </c>
       <c r="L20" s="22">
-        <v>-2.5582376885837235</v>
+        <v>-2.5616229029431636</v>
       </c>
       <c r="M20" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N20" s="7"/>
       <c r="Z20" s="6">
@@ -59538,16 +59971,16 @@
         <v>80.657697926811082</v>
       </c>
       <c r="J21" s="22">
-        <v>92.2491255464613</v>
+        <v>92.205343440745878</v>
       </c>
       <c r="K21" s="22">
-        <v>88.041732973627546</v>
+        <v>87.994565653552684</v>
       </c>
       <c r="L21" s="22">
-        <v>-4.2073925728337542</v>
+        <v>-4.2107777871931944</v>
       </c>
       <c r="M21" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N21" s="8"/>
       <c r="Z21" s="6">
@@ -59590,16 +60023,16 @@
         <v>149.98701781577574</v>
       </c>
       <c r="J22" s="22">
-        <v>172.30060647719367</v>
+        <v>172.25682437147825</v>
       </c>
       <c r="K22" s="22">
-        <v>157.37105286259222</v>
+        <v>157.32388554251733</v>
       </c>
       <c r="L22" s="22">
-        <v>-14.929553614601446</v>
+        <v>-14.932938828960914</v>
       </c>
       <c r="M22" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N22" s="7"/>
       <c r="Z22" s="6">
@@ -59642,16 +60075,16 @@
         <v>214.73722724327945</v>
       </c>
       <c r="J23" s="22">
-        <v>228.9714047240133</v>
+        <v>228.92762261829787</v>
       </c>
       <c r="K23" s="22">
-        <v>222.12126229009593</v>
+        <v>222.07409497002104</v>
       </c>
       <c r="L23" s="22">
-        <v>-6.8501424339173695</v>
+        <v>-6.8535276482768381</v>
       </c>
       <c r="M23" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N23" s="7"/>
       <c r="Z23" s="29">
@@ -59694,16 +60127,16 @@
         <v>238.65280503395857</v>
       </c>
       <c r="J24" s="22">
-        <v>263.30019012675183</v>
+        <v>263.25640802103641</v>
       </c>
       <c r="K24" s="22">
-        <v>246.03684008077505</v>
+        <v>245.98967276070016</v>
       </c>
       <c r="L24" s="22">
-        <v>-17.263350045976779</v>
+        <v>-17.266735260336247</v>
       </c>
       <c r="M24" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N24" s="7"/>
       <c r="Q24" s="3"/>
@@ -59747,16 +60180,16 @@
         <v>280.62137253692157</v>
       </c>
       <c r="J25" s="22">
-        <v>300.33791455050084</v>
+        <v>300.29413244478542</v>
       </c>
       <c r="K25" s="22">
-        <v>288.00540758373802</v>
+        <v>287.95824026366319</v>
       </c>
       <c r="L25" s="22">
-        <v>-12.332506966762821</v>
+        <v>-12.335892181122233</v>
       </c>
       <c r="M25" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N25" s="7"/>
       <c r="Z25" s="29">
@@ -59799,16 +60232,16 @@
         <v>354.04596224378224</v>
       </c>
       <c r="J26" s="22">
-        <v>303.32313139384269</v>
+        <v>303.27934928812726</v>
       </c>
       <c r="K26" s="22">
-        <v>361.42999729059869</v>
+        <v>361.38282997052386</v>
       </c>
       <c r="L26" s="22">
-        <v>58.106865896756005</v>
+        <v>58.103480682396594</v>
       </c>
       <c r="M26" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N26" s="7"/>
       <c r="Z26" s="29">
@@ -59851,16 +60284,16 @@
         <v>363.36142235493008</v>
       </c>
       <c r="J27" s="22">
-        <v>303.32313139384269</v>
+        <v>303.27934928812726</v>
       </c>
       <c r="K27" s="22">
-        <v>398.85880451809669</v>
+        <v>398.8116371980218</v>
       </c>
       <c r="L27" s="22">
-        <v>95.535673124254004</v>
+        <v>95.532287909894535</v>
       </c>
       <c r="M27" s="21">
-        <v>35.497382163166584</v>
+        <v>35.450214843091715</v>
       </c>
       <c r="N27" s="7"/>
       <c r="Z27" s="29">
@@ -59899,16 +60332,16 @@
         <v>347.46870028607333</v>
       </c>
       <c r="J28" s="22">
-        <v>303.32313139384269</v>
+        <v>303.27934928812726</v>
       </c>
       <c r="K28" s="22">
-        <v>383.26085077798257</v>
+        <v>383.21368345790773</v>
       </c>
       <c r="L28" s="22">
-        <v>79.937719384139882</v>
+        <v>79.93433416978047</v>
       </c>
       <c r="M28" s="21">
-        <v>35.792150491909254</v>
+        <v>35.744983171834384</v>
       </c>
       <c r="N28" s="7"/>
       <c r="AB28" s="2">
@@ -59945,16 +60378,16 @@
         <v>327.18133755537542</v>
       </c>
       <c r="J29" s="22">
-        <v>305.35027235124119</v>
+        <v>305.30649024552577</v>
       </c>
       <c r="K29" s="22">
-        <v>362.97348804728466</v>
+        <v>362.92632072720983</v>
       </c>
       <c r="L29" s="22">
-        <v>57.623215696043474</v>
+        <v>57.619830481684062</v>
       </c>
       <c r="M29" s="21">
-        <v>35.792150491909254</v>
+        <v>35.744983171834384</v>
       </c>
       <c r="N29" s="7"/>
     </row>
@@ -59987,16 +60420,16 @@
         <v>334.32606634132549</v>
       </c>
       <c r="J30" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K30" s="22">
-        <v>370.11821683323473</v>
+        <v>370.07104951315989</v>
       </c>
       <c r="L30" s="22">
-        <v>63.682129354476388</v>
+        <v>63.678744140116976</v>
       </c>
       <c r="M30" s="21">
-        <v>35.792150491909254</v>
+        <v>35.744983171834384</v>
       </c>
       <c r="N30" s="7"/>
     </row>
@@ -60029,16 +60462,16 @@
         <v>352.98211763964912</v>
       </c>
       <c r="J31" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K31" s="22">
-        <v>389.42688804439149</v>
+        <v>389.3797207243166</v>
       </c>
       <c r="L31" s="22">
-        <v>82.990800565633151</v>
+        <v>82.987415351273683</v>
       </c>
       <c r="M31" s="21">
-        <v>36.444770404742378</v>
+        <v>36.397603084667509</v>
       </c>
       <c r="N31" s="7"/>
     </row>
@@ -60071,16 +60504,16 @@
         <v>355.48980429575056</v>
       </c>
       <c r="J32" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K32" s="22">
-        <v>402.98939610334662</v>
+        <v>402.94222878327179</v>
       </c>
       <c r="L32" s="22">
-        <v>96.553308624588283</v>
+        <v>96.549923410228871</v>
       </c>
       <c r="M32" s="21">
-        <v>47.49959180759609</v>
+        <v>47.45242448752122</v>
       </c>
       <c r="N32" s="7"/>
     </row>
@@ -60113,16 +60546,16 @@
         <v>352.2715854433639</v>
       </c>
       <c r="J33" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K33" s="22">
-        <v>422.37345553914224</v>
+        <v>422.32628821906735</v>
       </c>
       <c r="L33" s="22">
-        <v>115.9373680603839</v>
+        <v>115.93398284602443</v>
       </c>
       <c r="M33" s="21">
-        <v>70.101870095778324</v>
+        <v>70.054702775703447</v>
       </c>
       <c r="N33" s="7"/>
     </row>
@@ -60155,16 +60588,16 @@
         <v>337.60137926289644</v>
       </c>
       <c r="J34" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K34" s="22">
-        <v>418.14489541840015</v>
+        <v>418.09772809832526</v>
       </c>
       <c r="L34" s="22">
-        <v>111.70880793964182</v>
+        <v>111.70542272528235</v>
       </c>
       <c r="M34" s="21">
-        <v>80.54351615550371</v>
+        <v>80.496348835428833</v>
       </c>
       <c r="N34" s="7"/>
     </row>
@@ -60197,16 +60630,16 @@
         <v>331.64813030229362</v>
       </c>
       <c r="J35" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K35" s="22">
-        <v>416.56731887978844</v>
+        <v>416.52015155971355</v>
       </c>
       <c r="L35" s="22">
-        <v>110.13123140103011</v>
+        <v>110.12784618667064</v>
       </c>
       <c r="M35" s="21">
-        <v>84.919188577494822</v>
+        <v>84.872021257419945</v>
       </c>
       <c r="N35" s="7"/>
     </row>
@@ -60239,16 +60672,16 @@
         <v>339.74634823900357</v>
       </c>
       <c r="J36" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K36" s="22">
-        <v>443.03688796494799</v>
+        <v>442.98972064487316</v>
       </c>
       <c r="L36" s="22">
-        <v>136.60080048618966</v>
+        <v>136.59741527183024</v>
       </c>
       <c r="M36" s="21">
-        <v>103.29053972594444</v>
+        <v>103.24337240586956</v>
       </c>
       <c r="N36" s="7"/>
       <c r="Q36" s="3"/>
@@ -60282,16 +60715,16 @@
         <v>126.76448886023145</v>
       </c>
       <c r="J37" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K37" s="22">
-        <v>486.16990261094327</v>
+        <v>486.12273529086843</v>
       </c>
       <c r="L37" s="22">
-        <v>179.73381513218493</v>
+        <v>179.73042991782552</v>
       </c>
       <c r="M37" s="21">
-        <v>359.40541375071183</v>
+        <v>359.358246430637</v>
       </c>
       <c r="N37" s="7"/>
     </row>
@@ -60324,16 +60757,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K38" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L38" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M38" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N38" s="7"/>
     </row>
@@ -60366,16 +60799,16 @@
         <v>0</v>
       </c>
       <c r="J39" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K39" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L39" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M39" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N39" s="7"/>
     </row>
@@ -60408,16 +60841,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K40" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L40" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M40" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N40" s="7"/>
     </row>
@@ -60450,16 +60883,16 @@
         <v>0</v>
       </c>
       <c r="J41" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K41" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L41" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M41" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N41" s="7"/>
     </row>
@@ -60492,16 +60925,16 @@
         <v>0</v>
       </c>
       <c r="J42" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K42" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L42" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M42" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N42" s="7"/>
     </row>
@@ -60534,16 +60967,16 @@
         <v>0</v>
       </c>
       <c r="J43" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K43" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L43" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M43" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N43" s="7"/>
     </row>
@@ -60576,16 +61009,16 @@
         <v>0</v>
       </c>
       <c r="J44" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K44" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L44" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M44" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N44" s="7"/>
     </row>
@@ -60618,16 +61051,16 @@
         <v>0</v>
       </c>
       <c r="J45" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K45" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L45" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M45" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N45" s="7"/>
     </row>
@@ -60660,16 +61093,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K46" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L46" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M46" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N46" s="7"/>
     </row>
@@ -60702,16 +61135,16 @@
         <v>0</v>
       </c>
       <c r="J47" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K47" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L47" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M47" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N47" s="7"/>
     </row>
@@ -60744,16 +61177,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K48" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L48" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M48" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N48" s="7"/>
     </row>
@@ -60786,16 +61219,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K49" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L49" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M49" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="14.1" customHeight="1">
@@ -60827,16 +61260,16 @@
         <v>0</v>
       </c>
       <c r="J50" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K50" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L50" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M50" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="14.1" customHeight="1">
@@ -60868,16 +61301,16 @@
         <v>0</v>
       </c>
       <c r="J51" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K51" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L51" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M51" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="14.1" customHeight="1">
@@ -60909,16 +61342,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K52" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L52" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M52" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="14.1" customHeight="1">
@@ -60950,16 +61383,16 @@
         <v>0</v>
       </c>
       <c r="J53" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K53" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L53" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M53" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="14.1" customHeight="1">
@@ -60991,16 +61424,16 @@
         <v>0</v>
       </c>
       <c r="J54" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K54" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L54" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M54" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="14.1" customHeight="1">
@@ -61032,16 +61465,16 @@
         <v>0</v>
       </c>
       <c r="J55" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K55" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L55" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M55" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="14.1" customHeight="1">
@@ -61073,16 +61506,16 @@
         <v>0</v>
       </c>
       <c r="J56" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K56" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L56" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M56" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="14.1" customHeight="1">
@@ -61114,16 +61547,16 @@
         <v>0</v>
       </c>
       <c r="J57" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K57" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L57" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M57" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="14.1" customHeight="1">
@@ -61155,16 +61588,16 @@
         <v>0</v>
       </c>
       <c r="J58" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K58" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L58" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M58" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="14.1" customHeight="1">
@@ -61196,16 +61629,16 @@
         <v>0</v>
       </c>
       <c r="J59" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K59" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L59" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M59" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="14.1" customHeight="1">
@@ -61237,16 +61670,16 @@
         <v>0</v>
       </c>
       <c r="J60" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K60" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L60" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M60" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="14.1" customHeight="1">
@@ -61278,16 +61711,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K61" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L61" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M61" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="14.1" customHeight="1">
@@ -61319,16 +61752,16 @@
         <v>0</v>
       </c>
       <c r="J62" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K62" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L62" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M62" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="14.1" customHeight="1">
@@ -61360,16 +61793,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K63" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L63" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M63" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="14.1" customHeight="1">
@@ -61401,16 +61834,16 @@
         <v>0.90153416025771216</v>
       </c>
       <c r="J64" s="22">
-        <v>307.33762163901605</v>
+        <v>307.29383953330063</v>
       </c>
       <c r="K64" s="22">
-        <v>498.90670154904672</v>
+        <v>498.85953422897182</v>
       </c>
       <c r="L64" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M64" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="14.1" customHeight="1">
@@ -61442,16 +61875,16 @@
         <v>1.1084914206975303</v>
       </c>
       <c r="J65" s="22">
-        <v>307.50765051667753</v>
+        <v>307.46386841096211</v>
       </c>
       <c r="K65" s="22">
-        <v>499.11365880948654</v>
+        <v>499.06649148941165</v>
       </c>
       <c r="L65" s="22">
-        <v>191.60600829280901</v>
+        <v>191.60262307844954</v>
       </c>
       <c r="M65" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="14.1" customHeight="1">
@@ -61483,16 +61916,16 @@
         <v>0.89446714184961917</v>
       </c>
       <c r="J66" s="22">
-        <v>307.50765051667753</v>
+        <v>307.46386841096211</v>
       </c>
       <c r="K66" s="22">
-        <v>499.19520733105378</v>
+        <v>499.14804001097889</v>
       </c>
       <c r="L66" s="22">
-        <v>191.68755681437625</v>
+        <v>191.68417160001678</v>
       </c>
       <c r="M66" s="21">
-        <v>498.30074018920413</v>
+        <v>498.25357286912924</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="14.1" customHeight="1">
@@ -61524,16 +61957,16 @@
         <v>0.85586449205052773</v>
       </c>
       <c r="J67" s="22">
-        <v>307.50765051667753</v>
+        <v>307.46386841096211</v>
       </c>
       <c r="K67" s="22">
-        <v>499.15743304036585</v>
+        <v>499.11026572029095</v>
       </c>
       <c r="L67" s="22">
-        <v>191.64978252368832</v>
+        <v>191.64639730932885</v>
       </c>
       <c r="M67" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="14.1" customHeight="1">
@@ -61565,16 +61998,16 @@
         <v>1.5788924406708102</v>
       </c>
       <c r="J68" s="22">
-        <v>308.28621714077974</v>
+        <v>308.24243503506432</v>
       </c>
       <c r="K68" s="22">
-        <v>499.88046098898616</v>
+        <v>499.83329366891127</v>
       </c>
       <c r="L68" s="22">
-        <v>191.59424384820642</v>
+        <v>191.59085863384695</v>
       </c>
       <c r="M68" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="14.1" customHeight="1">
@@ -61606,16 +62039,16 @@
         <v>6.7494303116673322</v>
       </c>
       <c r="J69" s="22">
-        <v>313.60003528991899</v>
+        <v>313.55625318420357</v>
       </c>
       <c r="K69" s="22">
-        <v>505.05099885998266</v>
+        <v>505.00383153990776</v>
       </c>
       <c r="L69" s="22">
-        <v>191.45096357006366</v>
+        <v>191.4475783557042</v>
       </c>
       <c r="M69" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="14.1" customHeight="1">
@@ -61647,16 +62080,16 @@
         <v>9.9133733862040057</v>
       </c>
       <c r="J70" s="22">
-        <v>316.4535834723722</v>
+        <v>316.40980136665678</v>
       </c>
       <c r="K70" s="22">
-        <v>508.21494193451935</v>
+        <v>508.16777461444445</v>
       </c>
       <c r="L70" s="22">
-        <v>191.76135846214714</v>
+        <v>191.75797324778767</v>
       </c>
       <c r="M70" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="14.1" customHeight="1">
@@ -61688,16 +62121,16 @@
         <v>10.495259866793916</v>
       </c>
       <c r="J71" s="22">
-        <v>316.71089770248</v>
+        <v>316.66711559676457</v>
       </c>
       <c r="K71" s="22">
-        <v>508.79682841510925</v>
+        <v>508.74966109503436</v>
       </c>
       <c r="L71" s="22">
-        <v>192.08593071262925</v>
+        <v>192.08254549826978</v>
       </c>
       <c r="M71" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="14.1" customHeight="1">
@@ -61729,16 +62162,16 @@
         <v>11.214216732390026</v>
       </c>
       <c r="J72" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K72" s="22">
-        <v>509.51578528070536</v>
+        <v>509.46861796063047</v>
       </c>
       <c r="L72" s="22">
-        <v>192.00037206169367</v>
+        <v>191.9969868473342</v>
       </c>
       <c r="M72" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="14.1" customHeight="1">
@@ -61770,16 +62203,16 @@
         <v>12.395947143481509</v>
       </c>
       <c r="J73" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K73" s="22">
-        <v>510.7754646513003</v>
+        <v>510.72829733122541</v>
       </c>
       <c r="L73" s="22">
-        <v>193.26005143228861</v>
+        <v>193.25666621792914</v>
       </c>
       <c r="M73" s="21">
-        <v>498.37951750781878</v>
+        <v>498.33235018774388</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="14.1" customHeight="1">
@@ -61811,16 +62244,16 @@
         <v>11.954148917418175</v>
       </c>
       <c r="J74" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K74" s="22">
-        <v>511.3962796036538</v>
+        <v>511.3491122835789</v>
       </c>
       <c r="L74" s="22">
-        <v>193.8808663846421</v>
+        <v>193.87748117028264</v>
       </c>
       <c r="M74" s="21">
-        <v>499.4421306862356</v>
+        <v>499.39496336616071</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="14.1" customHeight="1">
@@ -61852,16 +62285,16 @@
         <v>0</v>
       </c>
       <c r="J75" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K75" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L75" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M75" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="14.1" customHeight="1">
@@ -61893,16 +62326,16 @@
         <v>0</v>
       </c>
       <c r="J76" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K76" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L76" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M76" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="12.75">
@@ -61934,16 +62367,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K77" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L77" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M77" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="12.75">
@@ -61975,16 +62408,16 @@
         <v>0</v>
       </c>
       <c r="J78" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K78" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L78" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M78" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="12.75">
@@ -62016,16 +62449,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K79" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L79" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M79" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="12.75">
@@ -62057,16 +62490,16 @@
         <v>0</v>
       </c>
       <c r="J80" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K80" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L80" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M80" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="12.75">
@@ -62098,16 +62531,16 @@
         <v>0</v>
       </c>
       <c r="J81" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K81" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L81" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M81" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="12.75">
@@ -62139,16 +62572,16 @@
         <v>0.22000306970429231</v>
       </c>
       <c r="J82" s="22">
-        <v>317.73541628871601</v>
+        <v>317.69163418300059</v>
       </c>
       <c r="K82" s="22">
-        <v>513.4108061014947</v>
+        <v>513.36363878141981</v>
       </c>
       <c r="L82" s="22">
-        <v>195.67538981277869</v>
+        <v>195.67200459841922</v>
       </c>
       <c r="M82" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="12.75">
@@ -62180,16 +62613,16 @@
         <v>0.2309647808611083</v>
       </c>
       <c r="J83" s="22">
-        <v>317.74076568201389</v>
+        <v>317.69698357629846</v>
       </c>
       <c r="K83" s="22">
-        <v>513.42176781265152</v>
+        <v>513.37460049257663</v>
       </c>
       <c r="L83" s="22">
-        <v>195.68100213063764</v>
+        <v>195.67761691627817</v>
       </c>
       <c r="M83" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="12.75">
@@ -62221,16 +62654,16 @@
         <v>0.2476046408781975</v>
       </c>
       <c r="J84" s="22">
-        <v>317.75778856327963</v>
+        <v>317.71400645756421</v>
       </c>
       <c r="K84" s="22">
-        <v>513.43840767266863</v>
+        <v>513.39124035259374</v>
       </c>
       <c r="L84" s="22">
-        <v>195.680619109389</v>
+        <v>195.67723389502953</v>
       </c>
       <c r="M84" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="12.75">
@@ -62262,16 +62695,16 @@
         <v>28.570048006998732</v>
       </c>
       <c r="J85" s="22">
-        <v>346.12732616203544</v>
+        <v>346.08354405632002</v>
       </c>
       <c r="K85" s="22">
-        <v>541.76085103878916</v>
+        <v>541.71368371871426</v>
       </c>
       <c r="L85" s="22">
-        <v>195.63352487675371</v>
+        <v>195.63013966239424</v>
       </c>
       <c r="M85" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="12.75">
@@ -62303,16 +62736,16 @@
         <v>35.12375088595347</v>
       </c>
       <c r="J86" s="22">
-        <v>346.35166585996393</v>
+        <v>346.30788375424851</v>
       </c>
       <c r="K86" s="22">
-        <v>548.31455391774386</v>
+        <v>548.26738659766897</v>
       </c>
       <c r="L86" s="22">
-        <v>201.96288805777994</v>
+        <v>201.95950284342047</v>
       </c>
       <c r="M86" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="12.75">
@@ -62344,16 +62777,16 @@
         <v>35.2327855054628</v>
       </c>
       <c r="J87" s="22">
-        <v>346.43120812626563</v>
+        <v>346.38742602055021</v>
       </c>
       <c r="K87" s="22">
-        <v>548.42358853725318</v>
+        <v>548.3764212171784</v>
       </c>
       <c r="L87" s="22">
-        <v>201.99238041098755</v>
+        <v>201.9889951966282</v>
       </c>
       <c r="M87" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="12.75">
@@ -62385,16 +62818,16 @@
         <v>35.979887486370352</v>
       </c>
       <c r="J88" s="22">
-        <v>346.43120812626563</v>
+        <v>346.38742602055021</v>
       </c>
       <c r="K88" s="22">
-        <v>549.25120419774407</v>
+        <v>549.20403687766918</v>
       </c>
       <c r="L88" s="22">
-        <v>202.81999607147844</v>
+        <v>202.81661085711897</v>
       </c>
       <c r="M88" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="12.75">
@@ -62426,16 +62859,16 @@
         <v>34.671329374135034</v>
       </c>
       <c r="J89" s="22">
-        <v>347.15757819781584</v>
+        <v>347.11379609210042</v>
       </c>
       <c r="K89" s="22">
-        <v>547.94264608550873</v>
+        <v>547.89547876543384</v>
       </c>
       <c r="L89" s="22">
-        <v>200.78506788769289</v>
+        <v>200.78168267333342</v>
       </c>
       <c r="M89" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="12.75">
@@ -62467,16 +62900,16 @@
         <v>35.503258636049189</v>
       </c>
       <c r="J90" s="22">
-        <v>347.83889366468429</v>
+        <v>347.79511155896887</v>
       </c>
       <c r="K90" s="22">
-        <v>548.77457534742291</v>
+        <v>548.72740802734802</v>
       </c>
       <c r="L90" s="22">
-        <v>200.93568168273862</v>
+        <v>200.93229646837915</v>
       </c>
       <c r="M90" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="12.75">
@@ -62508,16 +62941,16 @@
         <v>36.308325460441139</v>
       </c>
       <c r="J91" s="22">
-        <v>348.92037187089284</v>
+        <v>348.87658976517741</v>
       </c>
       <c r="K91" s="22">
-        <v>549.57964217181484</v>
+        <v>549.53247485173995</v>
       </c>
       <c r="L91" s="22">
-        <v>200.659270300922</v>
+        <v>200.65588508656253</v>
       </c>
       <c r="M91" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="12.75">
@@ -62549,16 +62982,16 @@
         <v>50.522807320120393</v>
       </c>
       <c r="J92" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K92" s="22">
-        <v>563.79412403149411</v>
+        <v>563.74695671141922</v>
       </c>
       <c r="L92" s="22">
-        <v>197.36714737913957</v>
+        <v>197.3637621647801</v>
       </c>
       <c r="M92" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="12.75">
@@ -62590,16 +63023,16 @@
         <v>37.983849564585157</v>
       </c>
       <c r="J93" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K93" s="22">
-        <v>576.14629645503999</v>
+        <v>576.0991291349651</v>
       </c>
       <c r="L93" s="22">
-        <v>209.71931980268545</v>
+        <v>209.71593458832598</v>
       </c>
       <c r="M93" s="21">
-        <v>538.16244689045482</v>
+        <v>538.11527957037993</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="12.75">
@@ -62631,16 +63064,16 @@
         <v>0</v>
       </c>
       <c r="J94" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K94" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L94" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M94" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="12.75">
@@ -62672,16 +63105,16 @@
         <v>0</v>
       </c>
       <c r="J95" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K95" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L95" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M95" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="12.75">
@@ -62713,16 +63146,16 @@
         <v>0</v>
       </c>
       <c r="J96" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K96" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L96" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M96" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="12.75">
@@ -62754,16 +63187,16 @@
         <v>0</v>
       </c>
       <c r="J97" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K97" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L97" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M97" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="12.75">
@@ -62795,16 +63228,16 @@
         <v>0</v>
       </c>
       <c r="J98" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K98" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L98" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M98" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="12.75">
@@ -62836,16 +63269,16 @@
         <v>0</v>
       </c>
       <c r="J99" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K99" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L99" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M99" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="12.75">
@@ -62877,16 +63310,16 @@
         <v>0</v>
       </c>
       <c r="J100" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K100" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L100" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M100" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="12.75">
@@ -62918,16 +63351,16 @@
         <v>0</v>
       </c>
       <c r="J101" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K101" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L101" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M101" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="12.75">
@@ -62959,16 +63392,16 @@
         <v>0</v>
       </c>
       <c r="J102" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K102" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L102" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M102" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="12.75">
@@ -63000,16 +63433,16 @@
         <v>0</v>
       </c>
       <c r="J103" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K103" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L103" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M103" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="12.75">
@@ -63041,16 +63474,16 @@
         <v>0</v>
       </c>
       <c r="J104" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K104" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L104" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M104" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="12.75">
@@ -63082,16 +63515,16 @@
         <v>0</v>
       </c>
       <c r="J105" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K105" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L105" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M105" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="12.75">
@@ -63123,16 +63556,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K106" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L106" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M106" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="12.75">
@@ -63164,16 +63597,16 @@
         <v>0</v>
       </c>
       <c r="J107" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K107" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L107" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M107" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="12.75">
@@ -63205,16 +63638,16 @@
         <v>0</v>
       </c>
       <c r="J108" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K108" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L108" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M108" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="12.75">
@@ -63246,16 +63679,16 @@
         <v>0</v>
       </c>
       <c r="J109" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K109" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L109" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M109" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
   </sheetData>
